--- a/employee_information_forms/036_staff_induction--employee_information_forms.xlsx
+++ b/employee_information_forms/036_staff_induction--employee_information_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>emergency_contact_other_details</t>
+          <t>emergency_contact_other_details_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other Emergency Contact Details</t>
+          <t>Emergency Contact Other Details 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>emergency_contact_other_phone</t>
+          <t>emergency_contact_other_phone_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other Emergency Contact Phone</t>
+          <t>Emergency Contact Other Phone 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>emergency_contact_other_email</t>
+          <t>emergency_contact_other_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other Emergency Contact Email</t>
+          <t>Emergency Contact Other Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>emergency_contact_other_address</t>
+          <t>emergency_contact_other_address_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other Emergency Contact Address</t>
+          <t>Emergency Contact Other Address 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>emergency_contact_other_details</t>
+          <t>emergency_contact_other_details_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>emergency_contact_other_relationship_employer</t>
+          <t>emergency_contact_other_relationship_employer_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other Emergency Contact Relationship with Employer</t>
+          <t>Emergency Contact Other Relationship Employer 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
